--- a/files/九龙-红磡-必嘉坊．曦汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．曦汇.xlsx
@@ -14659,7 +14659,7 @@
         </is>
       </c>
       <c r="E306" s="4" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F306" s="3" t="inlineStr">
         <is>
@@ -14668,14 +14668,14 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
         <v>4563100</v>
       </c>
       <c r="I306" s="5" t="n">
-        <v>20932</v>
+        <v>21028</v>
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
@@ -18370,10 +18370,10 @@
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
-          <t>F | 218呎 (开放式)
+          <t>F | 217呎 (开放式)
 $456万
-$20,932/呎
-(26年-06月)</t>
+$21,028/呎
+(26年-07月)</t>
         </is>
       </c>
       <c r="H26" s="16" t="inlineStr">

--- a/files/九龙-红磡-必嘉坊．曦汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．曦汇.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="必嘉坊．曦汇 销控表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="必嘉坊．曦汇" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,14 +44,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -63,7 +68,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -74,7 +79,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -85,7 +90,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -95,9 +100,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -145,8 +171,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,19 +219,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -223,10 +237,34 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -607,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -15650,187 +15688,187 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>必嘉坊．曦汇 - 必嘉坊．曦汇 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>必嘉坊．曦汇 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>324 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>51 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>273 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K4" s="19" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L4" s="19" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M4" s="19" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N4" s="19" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O4" s="19" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P4" s="19" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 504呎 (2房)
 招标单位
@@ -15838,17 +15876,17 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>B | 569呎 (3房)
-$1,700万
+$1700万
 $29,877/呎
 (26年-04月)</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr"/>
-      <c r="E6" s="18" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr"/>
+      <c r="E5" s="22" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 383呎 (1房)
 招标单位
@@ -15856,9 +15894,9 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr"/>
-      <c r="H6" s="18" t="inlineStr"/>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="G5" s="22" t="inlineStr"/>
+      <c r="H5" s="22" t="inlineStr"/>
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>H | 544呎 (2房)
 招标单位
@@ -15866,16 +15904,16 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>J | 468呎 (2房)
-$1,409万
+$1409万
 $30,100/呎
 (26年-04月)</t>
         </is>
       </c>
-      <c r="K6" s="18" t="inlineStr"/>
-      <c r="L6" s="16" t="inlineStr">
+      <c r="K5" s="22" t="inlineStr"/>
+      <c r="L5" s="20" t="inlineStr">
         <is>
           <t>L | 223呎 (1房)
 招标单位
@@ -15883,7 +15921,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M6" s="16" t="inlineStr">
+      <c r="M5" s="20" t="inlineStr">
         <is>
           <t>M | 223呎 (1房)
 招标单位
@@ -15891,7 +15929,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="N6" s="16" t="inlineStr">
+      <c r="N5" s="20" t="inlineStr">
         <is>
           <t>N | 237呎 (1房)
 招标单位
@@ -15899,7 +15937,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="O6" s="16" t="inlineStr">
+      <c r="O5" s="20" t="inlineStr">
         <is>
           <t>P | 241呎 (1房)
 招标单位
@@ -15907,15 +15945,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P6" s="18" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="P5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 362呎 (2房)
 $890万
@@ -15923,7 +15961,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 275呎 (1房)
 $705万
@@ -15931,7 +15969,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 202呎 (开放式)
 $541万
@@ -15939,7 +15977,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>D | 202呎 (开放式)
 $467万
@@ -15947,7 +15985,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
 $506万
@@ -15955,7 +15993,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>F | 218呎 (开放式)
 $494万
@@ -15963,7 +16001,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>G | 339呎 (1房)
 $863万
@@ -15971,7 +16009,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr">
         <is>
           <t>H | 368呎 (2房)
 $936万
@@ -15979,7 +16017,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t>J | 270呎 (1房)
 $684万
@@ -15987,7 +16025,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K7" s="17" t="inlineStr">
+      <c r="K6" s="21" t="inlineStr">
         <is>
           <t>K | 270呎 (1房)
 $516万
@@ -15995,7 +16033,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t>L | 251呎 (1房)
 $612万
@@ -16003,7 +16041,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M7" s="17" t="inlineStr">
+      <c r="M6" s="21" t="inlineStr">
         <is>
           <t>M | 251呎 (1房)
 $651万
@@ -16011,7 +16049,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t>N | 266呎 (1房)
 $511万
@@ -16019,7 +16057,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="O7" s="17" t="inlineStr">
+      <c r="O6" s="21" t="inlineStr">
         <is>
           <t>P | 269呎 (1房)
 $576万
@@ -16027,7 +16065,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t>Q | 269呎 (1房)
 $669万
@@ -16036,13 +16074,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 362呎 (2房)
 $934万
@@ -16050,7 +16088,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 275呎 (1房)
 $681万
@@ -16058,7 +16096,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 202呎 (开放式)
 $539万
@@ -16066,7 +16104,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 202呎 (开放式)
 $536万
@@ -16074,7 +16112,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
 $462万
@@ -16082,7 +16120,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 218呎 (开放式)
 $567万
@@ -16090,7 +16128,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 339呎 (1房)
 $710万
@@ -16098,7 +16136,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="I8" s="17" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>H | 369呎 (2房)
 $931万
@@ -16106,7 +16144,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>J | 270呎 (1房)
 $682万
@@ -16114,7 +16152,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K8" s="17" t="inlineStr">
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>K | 270呎 (1房)
 $515万
@@ -16122,7 +16160,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t>L | 251呎 (1房)
 $636万
@@ -16130,7 +16168,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="M8" s="17" t="inlineStr">
+      <c r="M7" s="21" t="inlineStr">
         <is>
           <t>M | 251呎 (1房)
 $486万
@@ -16138,7 +16176,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t>N | 266呎 (1房)
 $509万
@@ -16146,7 +16184,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="O8" s="17" t="inlineStr">
+      <c r="O7" s="21" t="inlineStr">
         <is>
           <t>P | 269呎 (1房)
 $688万
@@ -16154,7 +16192,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t>Q | 269呎 (1房)
 $667万
@@ -16163,13 +16201,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 362呎 (2房)
 $922万
@@ -16177,7 +16215,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 276呎 (1房)
 $524万
@@ -16185,7 +16223,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 202呎 (开放式)
 $538万
@@ -16193,7 +16231,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>D | 202呎 (开放式)
 $464万
@@ -16201,7 +16239,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
 $437万
@@ -16209,7 +16247,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 218呎 (开放式)
 $565万
@@ -16217,7 +16255,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>G | 339呎 (1房)
 $635万
@@ -16225,7 +16263,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="I8" s="21" t="inlineStr">
         <is>
           <t>H | 368呎 (2房)
 $938万
@@ -16233,7 +16271,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t>J | 270呎 (1房)
 $702万
@@ -16241,7 +16279,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K9" s="17" t="inlineStr">
+      <c r="K8" s="21" t="inlineStr">
         <is>
           <t>K | 270呎 (1房)
 $513万
@@ -16249,7 +16287,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t>L | 251呎 (1房)
 $634万
@@ -16257,7 +16295,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M9" s="17" t="inlineStr">
+      <c r="M8" s="21" t="inlineStr">
         <is>
           <t>M | 251呎 (1房)
 $484万
@@ -16265,7 +16303,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t>N | 266呎 (1房)
 $508万
@@ -16273,7 +16311,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="O9" s="17" t="inlineStr">
+      <c r="O8" s="21" t="inlineStr">
         <is>
           <t>P | 269呎 (1房)
 $659万
@@ -16281,7 +16319,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="P8" s="21" t="inlineStr">
         <is>
           <t>Q | 269呎 (1房)
 $665万
@@ -16290,13 +16328,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 362呎 (2房)
 $919万
@@ -16304,7 +16342,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 276呎 (1房)
 $523万
@@ -16312,7 +16350,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 202呎 (开放式)
 $536万
@@ -16320,7 +16358,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 202呎 (开放式)
 $532万
@@ -16328,7 +16366,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
 $436万
@@ -16336,7 +16374,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 218呎 (开放式)
 $563万
@@ -16344,7 +16382,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>G | 339呎 (1房)
 $845万
@@ -16352,7 +16390,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="I9" s="21" t="inlineStr">
         <is>
           <t>H | 368呎 (2房)
 $791万
@@ -16360,7 +16398,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t>J | 270呎 (1房)
 $699万
@@ -16368,7 +16406,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K10" s="17" t="inlineStr">
+      <c r="K9" s="21" t="inlineStr">
         <is>
           <t>K | 270呎 (1房)
 $517万
@@ -16376,7 +16414,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t>L | 251呎 (1房)
 $613万
@@ -16384,7 +16422,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M10" s="17" t="inlineStr">
+      <c r="M9" s="21" t="inlineStr">
         <is>
           <t>M | 251呎 (1房)
 $567万
@@ -16392,7 +16430,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t>N | 266呎 (1房)
 $506万
@@ -16400,7 +16438,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="O10" s="17" t="inlineStr">
+      <c r="O9" s="21" t="inlineStr">
         <is>
           <t>P | 269呎 (1房)
 $684万
@@ -16408,7 +16446,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t>Q | 269呎 (1房)
 $684万
@@ -16417,13 +16455,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 362呎 (2房)
 $772万
@@ -16431,7 +16469,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 275呎 (1房)
 $682万
@@ -16439,7 +16477,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 202呎 (开放式)
 $535万
@@ -16447,7 +16485,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 202呎 (开放式)
 $525万
@@ -16455,7 +16493,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
 $458万
@@ -16463,7 +16501,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 218呎 (开放式)
 $562万
@@ -16471,7 +16509,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>G | 339呎 (1房)
 $741万
@@ -16479,7 +16517,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I10" s="21" t="inlineStr">
         <is>
           <t>H | 369呎 (2房)
 $923万
@@ -16487,7 +16525,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t>J | 270呎 (1房)
 $697万
@@ -16495,7 +16533,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K11" s="17" t="inlineStr">
+      <c r="K10" s="21" t="inlineStr">
         <is>
           <t>K | 270呎 (1房)
 $510万
@@ -16503,7 +16541,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t>L | 251呎 (1房)
 $630万
@@ -16511,7 +16549,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M11" s="17" t="inlineStr">
+      <c r="M10" s="21" t="inlineStr">
         <is>
           <t>M | 251呎 (1房)
 $481万
@@ -16519,7 +16557,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t>N | 266呎 (1房)
 $563万
@@ -16527,7 +16565,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="O11" s="17" t="inlineStr">
+      <c r="O10" s="21" t="inlineStr">
         <is>
           <t>P | 269呎 (1房)
 $689万
@@ -16535,7 +16573,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t>Q | 269呎 (1房)
 $654万
@@ -16544,13 +16582,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 362呎 (2房)
 $901万
@@ -16558,7 +16596,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 276呎 (1房)
 $580万
@@ -16566,7 +16604,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 201呎 (开放式)
 $464万
@@ -16574,7 +16612,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>D | 202呎 (开放式)
 $460万
@@ -16582,7 +16620,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
 $525万
@@ -16590,7 +16628,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 218呎 (开放式)
 $560万
@@ -16598,7 +16636,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>G | 339呎 (1房)
 $642万
@@ -16606,7 +16644,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="I11" s="21" t="inlineStr">
         <is>
           <t>H | 368呎 (2房)
 $921万
@@ -16614,7 +16652,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t>J | 270呎 (1房)
 $695万
@@ -16622,7 +16660,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K12" s="17" t="inlineStr">
+      <c r="K11" s="21" t="inlineStr">
         <is>
           <t>K | 270呎 (1房)
 $680万
@@ -16630,7 +16668,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t>L | 251呎 (1房)
 $629万
@@ -16638,7 +16676,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="M12" s="17" t="inlineStr">
+      <c r="M11" s="21" t="inlineStr">
         <is>
           <t>M | 251呎 (1房)
 $480万
@@ -16646,7 +16684,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t>N | 266呎 (1房)
 $504万
@@ -16654,7 +16692,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="O12" s="17" t="inlineStr">
+      <c r="O11" s="21" t="inlineStr">
         <is>
           <t>P | 269呎 (1房)
 $680万
@@ -16662,7 +16700,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="P11" s="21" t="inlineStr">
         <is>
           <t>Q | 269呎 (1房)
 $680万
@@ -16671,13 +16709,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 362呎 (2房)
 $862万
@@ -16685,7 +16723,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 276呎 (1房)
 $578万
@@ -16693,7 +16731,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 201呎 (开放式)
 $462万
@@ -16701,7 +16739,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 202呎 (开放式)
 $501万
@@ -16709,7 +16747,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
 $523万
@@ -16717,7 +16755,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 218呎 (开放式)
 $558万
@@ -16725,7 +16763,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>G | 339呎 (1房)
 $700万
@@ -16733,7 +16771,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="I12" s="21" t="inlineStr">
         <is>
           <t>H | 369呎 (2房)
 $890万
@@ -16741,7 +16779,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t>J | 270呎 (1房)
 $609万
@@ -16749,7 +16787,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="K13" s="17" t="inlineStr">
+      <c r="K12" s="21" t="inlineStr">
         <is>
           <t>K | 270呎 (1房)
 $650万
@@ -16757,7 +16795,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t>L | 251呎 (1房)
 $551万
@@ -16765,7 +16803,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="M13" s="17" t="inlineStr">
+      <c r="M12" s="21" t="inlineStr">
         <is>
           <t>M | 251呎 (1房)
 $484万
@@ -16773,7 +16811,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t>N | 266呎 (1房)
 $502万
@@ -16781,7 +16819,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="O13" s="17" t="inlineStr">
+      <c r="O12" s="21" t="inlineStr">
         <is>
           <t>P | 269呎 (1房)
 $678万
@@ -16789,7 +16827,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="P12" s="21" t="inlineStr">
         <is>
           <t>Q | 269呎 (1房)
 $678万
@@ -16798,13 +16836,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 362呎 (2房)
 $860万
@@ -16812,7 +16850,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 276呎 (1房)
 $576万
@@ -16820,7 +16858,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 202呎 (开放式)
 $525万
@@ -16828,7 +16866,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 202呎 (开放式)
 $450万
@@ -16836,7 +16874,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
 $522万
@@ -16844,7 +16882,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>F | 217呎 (开放式)
 $484万
@@ -16852,7 +16890,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>G | 339呎 (1房)
 $625万
@@ -16860,7 +16898,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="I14" s="17" t="inlineStr">
+      <c r="I13" s="21" t="inlineStr">
         <is>
           <t>H | 369呎 (2房)
 $934万
@@ -16868,7 +16906,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t>J | 270呎 (1房)
 $677万
@@ -16876,7 +16914,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K14" s="17" t="inlineStr">
+      <c r="K13" s="21" t="inlineStr">
         <is>
           <t>K | 270呎 (1房)
 $648万
@@ -16884,7 +16922,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t>L | 251呎 (1房)
 $600万
@@ -16892,7 +16930,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M14" s="17" t="inlineStr">
+      <c r="M13" s="21" t="inlineStr">
         <is>
           <t>M | 251呎 (1房)
 $477万
@@ -16900,7 +16938,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t>N | 266呎 (1房)
 $500万
@@ -16908,7 +16946,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="O14" s="17" t="inlineStr">
+      <c r="O13" s="21" t="inlineStr">
         <is>
           <t>P | 269呎 (1房)
 $676万
@@ -16916,7 +16954,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t>Q | 269呎 (1房)
 $675万
@@ -16925,13 +16963,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 362呎 (2房)
 $866万
@@ -16939,7 +16977,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 276呎 (1房)
 $604万
@@ -16947,7 +16985,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 201呎 (开放式)
 $460万
@@ -16955,7 +16993,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 202呎 (开放式)
 $456万
@@ -16963,7 +17001,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
 $494万
@@ -16971,7 +17009,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 218呎 (开放式)
 $555万
@@ -16979,7 +17017,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>G | 339呎 (1房)
 $732万
@@ -16987,7 +17025,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="I14" s="21" t="inlineStr">
         <is>
           <t>H | 368呎 (2房)
 $704万
@@ -16995,7 +17033,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t>J | 270呎 (1房)
 $575万
@@ -17003,7 +17041,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="K15" s="17" t="inlineStr">
+      <c r="K14" s="21" t="inlineStr">
         <is>
           <t>K | 270呎 (1房)
 $504万
@@ -17011,7 +17049,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t>L | 251呎 (1房)
 $623万
@@ -17019,7 +17057,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M15" s="17" t="inlineStr">
+      <c r="M14" s="21" t="inlineStr">
         <is>
           <t>M | 251呎 (1房)
 $476万
@@ -17027,7 +17065,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="N15" s="17" t="inlineStr">
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t>N | 266呎 (1房)
 $582万
@@ -17035,7 +17073,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="O15" s="17" t="inlineStr">
+      <c r="O14" s="21" t="inlineStr">
         <is>
           <t>P | 269呎 (1房)
 $681万
@@ -17043,7 +17081,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="P15" s="17" t="inlineStr">
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t>Q | 269呎 (1房)
 $673万
@@ -17052,13 +17090,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 362呎 (2房)
 $890万
@@ -17066,7 +17104,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 275呎 (1房)
 $686万
@@ -17074,7 +17112,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 201呎 (开放式)
 $452万
@@ -17082,7 +17120,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 202呎 (开放式)
 $455万
@@ -17090,7 +17128,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
 $492万
@@ -17098,7 +17136,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 218呎 (开放式)
 $553万
@@ -17106,7 +17144,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t>G | 339呎 (1房)
 $730万
@@ -17114,7 +17152,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I15" s="21" t="inlineStr">
         <is>
           <t>H | 368呎 (2房)
 $688万
@@ -17122,7 +17160,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="J16" s="17" t="inlineStr">
+      <c r="J15" s="21" t="inlineStr">
         <is>
           <t>J | 270呎 (1房)
 $604万
@@ -17130,7 +17168,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="K16" s="17" t="inlineStr">
+      <c r="K15" s="21" t="inlineStr">
         <is>
           <t>K | 270呎 (1房)
 $590万
@@ -17138,7 +17176,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="L16" s="17" t="inlineStr">
+      <c r="L15" s="21" t="inlineStr">
         <is>
           <t>L | 251呎 (1房)
 $621万
@@ -17146,7 +17184,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M16" s="17" t="inlineStr">
+      <c r="M15" s="21" t="inlineStr">
         <is>
           <t>M | 251呎 (1房)
 $634万
@@ -17154,7 +17192,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="N16" s="17" t="inlineStr">
+      <c r="N15" s="21" t="inlineStr">
         <is>
           <t>N | 266呎 (1房)
 $665万
@@ -17162,7 +17200,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="O16" s="17" t="inlineStr">
+      <c r="O15" s="21" t="inlineStr">
         <is>
           <t>P | 269呎 (1房)
 $645万
@@ -17170,7 +17208,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P16" s="17" t="inlineStr">
+      <c r="P15" s="21" t="inlineStr">
         <is>
           <t>Q | 269呎 (1房)
 $671万
@@ -17179,13 +17217,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 362呎 (2房)
 $888万
@@ -17193,7 +17231,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 276呎 (1房)
 $601万
@@ -17201,7 +17239,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 202呎 (开放式)
 $518万
@@ -17209,7 +17247,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 202呎 (开放式)
 $454万
@@ -17217,7 +17255,7 @@
 (26年-07月)</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
 $442万
@@ -17225,7 +17263,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>F | 217呎 (开放式)
 $480万
@@ -17233,7 +17271,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>G | 339呎 (1房)
 $728万
@@ -17241,7 +17279,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="I17" s="17" t="inlineStr">
+      <c r="I16" s="21" t="inlineStr">
         <is>
           <t>H | 368呎 (2房)
 $686万
@@ -17249,7 +17287,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="J17" s="17" t="inlineStr">
+      <c r="J16" s="21" t="inlineStr">
         <is>
           <t>J | 270呎 (1房)
 $513万
@@ -17257,7 +17295,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="K17" s="17" t="inlineStr">
+      <c r="K16" s="21" t="inlineStr">
         <is>
           <t>K | 270呎 (1房)
 $501万
@@ -17265,7 +17303,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="L16" s="21" t="inlineStr">
         <is>
           <t>L | 251呎 (1房)
 $594万
@@ -17273,7 +17311,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M17" s="17" t="inlineStr">
+      <c r="M16" s="21" t="inlineStr">
         <is>
           <t>M | 251呎 (1房)
 $555万
@@ -17281,7 +17319,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="N17" s="17" t="inlineStr">
+      <c r="N16" s="21" t="inlineStr">
         <is>
           <t>N | 266呎 (1房)
 $496万
@@ -17289,7 +17327,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="O17" s="17" t="inlineStr">
+      <c r="O16" s="21" t="inlineStr">
         <is>
           <t>P | 269呎 (1房)
 $670万
@@ -17297,7 +17335,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P17" s="17" t="inlineStr">
+      <c r="P16" s="21" t="inlineStr">
         <is>
           <t>Q | 269呎 (1房)
 $642万
@@ -17306,13 +17344,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 362呎 (2房)
 $882万
@@ -17320,7 +17358,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 276呎 (1房)
 $589万
@@ -17328,7 +17366,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 201呎 (开放式)
 $449万
@@ -17336,7 +17374,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 202呎 (开放式)
 $452万
@@ -17344,7 +17382,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
 $448万
@@ -17352,7 +17390,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 218呎 (开放式)
 $550万
@@ -17360,7 +17398,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 339呎 (1房)
 $834万
@@ -17368,7 +17406,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I18" s="17" t="inlineStr">
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t>H | 368呎 (2房)
 $803万
@@ -17376,7 +17414,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="J18" s="17" t="inlineStr">
+      <c r="J17" s="21" t="inlineStr">
         <is>
           <t>J | 270呎 (1房)
 $683万
@@ -17384,7 +17422,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K18" s="17" t="inlineStr">
+      <c r="K17" s="21" t="inlineStr">
         <is>
           <t>K | 270呎 (1房)
 $505万
@@ -17392,7 +17430,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="L18" s="17" t="inlineStr">
+      <c r="L17" s="21" t="inlineStr">
         <is>
           <t>L | 251呎 (1房)
 $593万
@@ -17400,7 +17438,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M18" s="17" t="inlineStr">
+      <c r="M17" s="21" t="inlineStr">
         <is>
           <t>M | 251呎 (1房)
 $554万
@@ -17408,7 +17446,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="N18" s="17" t="inlineStr">
+      <c r="N17" s="21" t="inlineStr">
         <is>
           <t>N | 266呎 (1房)
 $494万
@@ -17416,7 +17454,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="O18" s="17" t="inlineStr">
+      <c r="O17" s="21" t="inlineStr">
         <is>
           <t>P | 269呎 (1房)
 $587万
@@ -17424,7 +17462,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="P18" s="17" t="inlineStr">
+      <c r="P17" s="21" t="inlineStr">
         <is>
           <t>Q | 269呎 (1房)
 $640万
@@ -17433,13 +17471,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>A | 362呎 (2房)
 $881万
@@ -17447,7 +17485,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 276呎 (1房)
 $566万
@@ -17455,7 +17493,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 201呎 (开放式)
 $446万
@@ -17463,7 +17501,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>D | 202呎 (开放式)
 $449万
@@ -17471,7 +17509,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
 $423万
@@ -17479,7 +17517,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>F | 217呎 (开放式)
 $475万
@@ -17487,7 +17525,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 339呎 (1房)
 $831万
@@ -17495,7 +17533,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I19" s="17" t="inlineStr">
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>H | 368呎 (2房)
 $682万
@@ -17503,7 +17541,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="J19" s="17" t="inlineStr">
+      <c r="J18" s="21" t="inlineStr">
         <is>
           <t>J | 270呎 (1房)
 $667万
@@ -17511,7 +17549,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K19" s="17" t="inlineStr">
+      <c r="K18" s="21" t="inlineStr">
         <is>
           <t>K | 270呎 (1房)
 $498万
@@ -17519,7 +17557,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="L19" s="17" t="inlineStr">
+      <c r="L18" s="21" t="inlineStr">
         <is>
           <t>L | 251呎 (1房)
 $622万
@@ -17527,7 +17565,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="M19" s="17" t="inlineStr">
+      <c r="M18" s="21" t="inlineStr">
         <is>
           <t>M | 251呎 (1房)
 $552万
@@ -17535,7 +17573,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="N19" s="17" t="inlineStr">
+      <c r="N18" s="21" t="inlineStr">
         <is>
           <t>N | 266呎 (1房)
 $569万
@@ -17543,7 +17581,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="O19" s="17" t="inlineStr">
+      <c r="O18" s="21" t="inlineStr">
         <is>
           <t>P | 269呎 (1房)
 $586万
@@ -17551,7 +17589,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="P19" s="17" t="inlineStr">
+      <c r="P18" s="21" t="inlineStr">
         <is>
           <t>Q | 269呎 (1房)
 $585万
@@ -17560,13 +17598,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 362呎 (2房)
 $853万
@@ -17574,7 +17612,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 276呎 (1房)
 $559万
@@ -17582,7 +17620,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 201呎 (开放式)
 $441万
@@ -17590,7 +17628,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 202呎 (开放式)
 $510万
@@ -17598,7 +17636,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
 $506万
@@ -17606,7 +17644,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 218呎 (开放式)
 $540万
@@ -17614,7 +17652,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H20" s="17" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>G | 339呎 (1房)
 $717万
@@ -17622,7 +17660,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="I20" s="17" t="inlineStr">
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>H | 368呎 (2房)
 $676万
@@ -17630,7 +17668,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="J20" s="17" t="inlineStr">
+      <c r="J19" s="21" t="inlineStr">
         <is>
           <t>J | 270呎 (1房)
 $651万
@@ -17638,7 +17676,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K20" s="17" t="inlineStr">
+      <c r="K19" s="21" t="inlineStr">
         <is>
           <t>K | 270呎 (1房)
 $664万
@@ -17646,7 +17684,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L20" s="17" t="inlineStr">
+      <c r="L19" s="21" t="inlineStr">
         <is>
           <t>L | 251呎 (1房)
 $589万
@@ -17654,7 +17692,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M20" s="17" t="inlineStr">
+      <c r="M19" s="21" t="inlineStr">
         <is>
           <t>M | 251呎 (1房)
 $626万
@@ -17662,7 +17700,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N20" s="17" t="inlineStr">
+      <c r="N19" s="21" t="inlineStr">
         <is>
           <t>N | 266呎 (1房)
 $663万
@@ -17670,7 +17708,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O20" s="17" t="inlineStr">
+      <c r="O19" s="21" t="inlineStr">
         <is>
           <t>P | 269呎 (1房)
 $671万
@@ -17678,7 +17716,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P20" s="17" t="inlineStr">
+      <c r="P19" s="21" t="inlineStr">
         <is>
           <t>Q | 269呎 (1房)
 $663万
@@ -17687,13 +17725,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 362呎 (2房)
 $887万
@@ -17701,7 +17739,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 276呎 (1房)
 $553万
@@ -17709,7 +17747,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 201呎 (开放式)
 $437万
@@ -17717,7 +17755,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 202呎 (开放式)
 $506万
@@ -17725,7 +17763,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
 $429万
@@ -17733,7 +17771,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 218呎 (开放式)
 $535万
@@ -17741,7 +17779,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>G | 339呎 (1房)
 $712万
@@ -17749,7 +17787,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="I21" s="17" t="inlineStr">
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>H | 368呎 (2房)
 $671万
@@ -17757,7 +17795,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="J21" s="17" t="inlineStr">
+      <c r="J20" s="21" t="inlineStr">
         <is>
           <t>J | 270呎 (1房)
 $506万
@@ -17765,7 +17803,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="K21" s="17" t="inlineStr">
+      <c r="K20" s="21" t="inlineStr">
         <is>
           <t>K | 270呎 (1房)
 $662万
@@ -17773,7 +17811,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L21" s="17" t="inlineStr">
+      <c r="L20" s="21" t="inlineStr">
         <is>
           <t>L | 251呎 (1房)
 $618万
@@ -17781,7 +17819,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M21" s="17" t="inlineStr">
+      <c r="M20" s="21" t="inlineStr">
         <is>
           <t>M | 251呎 (1房)
 $631万
@@ -17789,7 +17827,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="N21" s="17" t="inlineStr">
+      <c r="N20" s="21" t="inlineStr">
         <is>
           <t>N | 266呎 (1房)
 $575万
@@ -17797,7 +17835,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="O21" s="17" t="inlineStr">
+      <c r="O20" s="21" t="inlineStr">
         <is>
           <t>P | 269呎 (1房)
 $662万
@@ -17805,7 +17843,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P21" s="17" t="inlineStr">
+      <c r="P20" s="21" t="inlineStr">
         <is>
           <t>Q | 269呎 (1房)
 $661万
@@ -17814,13 +17852,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 362呎 (2房)
 $876万
@@ -17828,7 +17866,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 276呎 (1房)
 $552万
@@ -17836,7 +17874,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 201呎 (开放式)
 $435万
@@ -17844,7 +17882,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 202呎 (开放式)
 $438万
@@ -17852,7 +17890,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
 $435万
@@ -17860,7 +17898,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 218呎 (开放式)
 $533万
@@ -17868,7 +17906,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 339呎 (1房)
 $816万
@@ -17876,7 +17914,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I22" s="17" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>H | 368呎 (2房)
 $669万
@@ -17884,7 +17922,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="J22" s="17" t="inlineStr">
+      <c r="J21" s="21" t="inlineStr">
         <is>
           <t>J | 270呎 (1房)
 $674万
@@ -17892,7 +17930,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K22" s="17" t="inlineStr">
+      <c r="K21" s="21" t="inlineStr">
         <is>
           <t>K | 270呎 (1房)
 $494万
@@ -17900,7 +17938,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="L22" s="17" t="inlineStr">
+      <c r="L21" s="21" t="inlineStr">
         <is>
           <t>L | 251呎 (1房)
 $592万
@@ -17908,7 +17946,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="M22" s="17" t="inlineStr">
+      <c r="M21" s="21" t="inlineStr">
         <is>
           <t>M | 251呎 (1房)
 $471万
@@ -17916,7 +17954,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="N22" s="17" t="inlineStr">
+      <c r="N21" s="21" t="inlineStr">
         <is>
           <t>N | 266呎 (1房)
 $574万
@@ -17924,7 +17962,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="O22" s="17" t="inlineStr">
+      <c r="O21" s="21" t="inlineStr">
         <is>
           <t>P | 269呎 (1房)
 $580万
@@ -17932,7 +17970,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="P22" s="17" t="inlineStr">
+      <c r="P21" s="21" t="inlineStr">
         <is>
           <t>Q | 269呎 (1房)
 $632万
@@ -17941,13 +17979,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 362呎 (2房)
 $847万
@@ -17955,7 +17993,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 275呎 (1房)
 $632万
@@ -17963,7 +18001,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 201呎 (开放式)
 $434万
@@ -17971,7 +18009,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 202呎 (开放式)
 $437万
@@ -17979,7 +18017,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
 $493万
@@ -17987,7 +18025,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 217呎 (开放式)
 $531万
@@ -17995,7 +18033,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>G | 339呎 (1房)
 $708万
@@ -18003,7 +18041,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="I23" s="17" t="inlineStr">
+      <c r="I22" s="21" t="inlineStr">
         <is>
           <t>H | 368呎 (2房)
 $667万
@@ -18011,7 +18049,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="J23" s="17" t="inlineStr">
+      <c r="J22" s="21" t="inlineStr">
         <is>
           <t>J | 270呎 (1房)
 $652万
@@ -18019,7 +18057,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K23" s="17" t="inlineStr">
+      <c r="K22" s="21" t="inlineStr">
         <is>
           <t>K | 270呎 (1房)
 $638万
@@ -18027,7 +18065,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L23" s="17" t="inlineStr">
+      <c r="L22" s="21" t="inlineStr">
         <is>
           <t>L | 251呎 (1房)
 $584万
@@ -18035,7 +18073,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M23" s="17" t="inlineStr">
+      <c r="M22" s="21" t="inlineStr">
         <is>
           <t>M | 251呎 (1房)
 $602万
@@ -18043,7 +18081,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="N23" s="17" t="inlineStr">
+      <c r="N22" s="21" t="inlineStr">
         <is>
           <t>N | 266呎 (1房)
 $572万
@@ -18051,7 +18089,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="O23" s="17" t="inlineStr">
+      <c r="O22" s="21" t="inlineStr">
         <is>
           <t>P | 269呎 (1房)
 $659万
@@ -18059,7 +18097,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P23" s="17" t="inlineStr">
+      <c r="P22" s="21" t="inlineStr">
         <is>
           <t>Q | 269呎 (1房)
 $657万
@@ -18068,13 +18106,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 362呎 (2房)
 $873万
@@ -18082,7 +18120,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 276呎 (1房)
 $579万
@@ -18090,7 +18128,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 201呎 (开放式)
 $434万
@@ -18098,7 +18136,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 202呎 (开放式)
 $437万
@@ -18106,7 +18144,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
 $473万
@@ -18114,7 +18152,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 218呎 (开放式)
 $531万
@@ -18122,7 +18160,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 339呎 (1房)
 $814万
@@ -18130,7 +18168,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I24" s="17" t="inlineStr">
+      <c r="I23" s="21" t="inlineStr">
         <is>
           <t>H | 368呎 (2房)
 $667万
@@ -18138,7 +18176,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="J24" s="17" t="inlineStr">
+      <c r="J23" s="21" t="inlineStr">
         <is>
           <t>J | 270呎 (1房)
 $645万
@@ -18146,7 +18184,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K24" s="17" t="inlineStr">
+      <c r="K23" s="21" t="inlineStr">
         <is>
           <t>K | 270呎 (1房)
 $657万
@@ -18154,7 +18192,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L24" s="17" t="inlineStr">
+      <c r="L23" s="21" t="inlineStr">
         <is>
           <t>L | 251呎 (1房)
 $608万
@@ -18162,7 +18200,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M24" s="17" t="inlineStr">
+      <c r="M23" s="21" t="inlineStr">
         <is>
           <t>M | 251呎 (1房)
 $545万
@@ -18170,7 +18208,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="N24" s="17" t="inlineStr">
+      <c r="N23" s="21" t="inlineStr">
         <is>
           <t>N | 266呎 (1房)
 $487万
@@ -18178,7 +18216,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="O24" s="17" t="inlineStr">
+      <c r="O23" s="21" t="inlineStr">
         <is>
           <t>P | 269呎 (1房)
 $659万
@@ -18186,7 +18224,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="P24" s="17" t="inlineStr">
+      <c r="P23" s="21" t="inlineStr">
         <is>
           <t>Q | 269呎 (1房)
 $657万
@@ -18195,13 +18233,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 362呎 (2房)
 $836万
@@ -18209,7 +18247,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 276呎 (1房)
 $546万
@@ -18217,7 +18255,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 201呎 (开放式)
 $431万
@@ -18225,7 +18263,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 202呎 (开放式)
 $499万
@@ -18233,7 +18271,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F25" s="17" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
 $475万
@@ -18241,7 +18279,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G25" s="17" t="inlineStr">
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>F | 218呎 (开放式)
 $459万
@@ -18249,7 +18287,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="H25" s="17" t="inlineStr">
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>G | 339呎 (1房)
 $704万
@@ -18257,7 +18295,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="I25" s="17" t="inlineStr">
+      <c r="I24" s="21" t="inlineStr">
         <is>
           <t>H | 368呎 (2房)
 $757万
@@ -18265,7 +18303,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="J25" s="17" t="inlineStr">
+      <c r="J24" s="21" t="inlineStr">
         <is>
           <t>J | 270呎 (1房)
 $677万
@@ -18273,7 +18311,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K25" s="17" t="inlineStr">
+      <c r="K24" s="21" t="inlineStr">
         <is>
           <t>K | 270呎 (1房)
 $628万
@@ -18281,7 +18319,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="L25" s="17" t="inlineStr">
+      <c r="L24" s="21" t="inlineStr">
         <is>
           <t>L | 251呎 (1房)
 $579万
@@ -18289,7 +18327,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M25" s="17" t="inlineStr">
+      <c r="M24" s="21" t="inlineStr">
         <is>
           <t>M | 251呎 (1房)
 $463万
@@ -18297,7 +18335,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="N25" s="17" t="inlineStr">
+      <c r="N24" s="21" t="inlineStr">
         <is>
           <t>N | 266呎 (1房)
 $649万
@@ -18305,7 +18343,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O25" s="17" t="inlineStr">
+      <c r="O24" s="21" t="inlineStr">
         <is>
           <t>P | 269呎 (1房)
 $657万
@@ -18313,7 +18351,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P25" s="17" t="inlineStr">
+      <c r="P24" s="21" t="inlineStr">
         <is>
           <t>Q | 269呎 (1房)
 $655万
@@ -18322,13 +18360,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 362呎 (2房)
 $866万
@@ -18336,7 +18374,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 276呎 (1房)
 $571万
@@ -18344,7 +18382,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 201呎 (开放式)
 $429万
@@ -18352,7 +18390,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 202呎 (开放式)
 $432万
@@ -18360,7 +18398,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
 $420万
@@ -18368,7 +18406,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="G26" s="17" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 217呎 (开放式)
 $456万
@@ -18376,7 +18414,7 @@
 (26年-07月)</t>
         </is>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>G | 339呎 (1房)
 $807万
@@ -18384,7 +18422,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I26" s="17" t="inlineStr">
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>H | 368呎 (2房)
 $774万
@@ -18392,7 +18430,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="J26" s="17" t="inlineStr">
+      <c r="J25" s="21" t="inlineStr">
         <is>
           <t>J | 270呎 (1房)
 $668万
@@ -18400,7 +18438,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="K26" s="17" t="inlineStr">
+      <c r="K25" s="21" t="inlineStr">
         <is>
           <t>K | 270呎 (1房)
 $627万
@@ -18408,7 +18446,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="L26" s="17" t="inlineStr">
+      <c r="L25" s="21" t="inlineStr">
         <is>
           <t>L | 251呎 (1房)
 $505万
@@ -18416,7 +18454,7 @@
 (23年-09月)</t>
         </is>
       </c>
-      <c r="M26" s="17" t="inlineStr">
+      <c r="M25" s="21" t="inlineStr">
         <is>
           <t>M | 251呎 (1房)
 $542万
@@ -18424,7 +18462,7 @@
 (23年-09月)</t>
         </is>
       </c>
-      <c r="N26" s="17" t="inlineStr">
+      <c r="N25" s="21" t="inlineStr">
         <is>
           <t>N | 266呎 (1房)
 $484万
@@ -18432,7 +18470,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="O26" s="17" t="inlineStr">
+      <c r="O25" s="21" t="inlineStr">
         <is>
           <t>P | 269呎 (1房)
 $655万
@@ -18440,7 +18478,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P26" s="17" t="inlineStr">
+      <c r="P25" s="21" t="inlineStr">
         <is>
           <t>Q | 269呎 (1房)
 $627万
@@ -18449,13 +18487,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 324呎 (2房)
 $890万
@@ -18463,7 +18501,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 237呎 (1房)
 $548万
@@ -18471,7 +18509,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 180呎 (开放式)
 $434万
@@ -18479,7 +18517,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 180呎 (开放式)
 $433万
@@ -18487,7 +18525,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 180呎 (开放式)
 $501万
@@ -18495,7 +18533,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 189呎 (开放式)
 $521万
@@ -18503,7 +18541,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 招标单位
@@ -18511,7 +18549,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I27" s="16" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>H | 331呎 (2房)
 招标单位
@@ -18519,7 +18557,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J27" s="16" t="inlineStr">
+      <c r="J26" s="20" t="inlineStr">
         <is>
           <t>J | 232呎 (1房)
 招标单位
@@ -18527,7 +18565,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K27" s="16" t="inlineStr">
+      <c r="K26" s="20" t="inlineStr">
         <is>
           <t>K | 233呎 (1房)
 招标单位
@@ -18535,7 +18573,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L27" s="17" t="inlineStr">
+      <c r="L26" s="21" t="inlineStr">
         <is>
           <t>L | 213呎 (1房)
 $677万
@@ -18543,7 +18581,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="M27" s="16" t="inlineStr">
+      <c r="M26" s="20" t="inlineStr">
         <is>
           <t>M | 213呎 (1房)
 招标单位
@@ -18551,7 +18589,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="N27" s="16" t="inlineStr">
+      <c r="N26" s="20" t="inlineStr">
         <is>
           <t>N | 228呎 (1房)
 招标单位
@@ -18559,7 +18597,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="O27" s="16" t="inlineStr">
+      <c r="O26" s="20" t="inlineStr">
         <is>
           <t>P | 232呎 (1房)
 招标单位
@@ -18567,7 +18605,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P27" s="16" t="inlineStr">
+      <c r="P26" s="20" t="inlineStr">
         <is>
           <t>Q | 232呎 (1房)
 招标单位
@@ -18578,7 +18616,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
